--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.97370611513428</v>
+        <v>5.358227243709321</v>
       </c>
       <c r="D2" t="n">
-        <v>32.90156925853859</v>
+        <v>5.346505004512521</v>
       </c>
       <c r="E2" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F2" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.55004464141321</v>
+        <v>10.16438225422965</v>
       </c>
       <c r="D3" t="n">
-        <v>63.12107805110084</v>
+        <v>10.25717518330389</v>
       </c>
       <c r="E3" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F3" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.75839285617755</v>
+        <v>11.01073883912885</v>
       </c>
       <c r="D4" t="n">
-        <v>67.58543474730473</v>
+        <v>10.98263314643702</v>
       </c>
       <c r="E4" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F4" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.94256912726057</v>
+        <v>3.565667483179842</v>
       </c>
       <c r="D5" t="n">
-        <v>25.34758371127315</v>
+        <v>4.118982353081887</v>
       </c>
       <c r="E5" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F5" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.33353447519272</v>
+        <v>2.491699352218817</v>
       </c>
       <c r="D6" t="n">
-        <v>19.1049731745428</v>
+        <v>3.104558140863205</v>
       </c>
       <c r="E6" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F6" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.94469593815793</v>
+        <v>3.728513089950665</v>
       </c>
       <c r="D7" t="n">
-        <v>26.26410072776978</v>
+        <v>4.26791636826259</v>
       </c>
       <c r="E7" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F7" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.33578404875463</v>
+        <v>1.842064907922628</v>
       </c>
       <c r="D8" t="n">
-        <v>17.18248622505476</v>
+        <v>2.792154011571399</v>
       </c>
       <c r="E8" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F8" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.36811210804346</v>
+        <v>3.309818217557062</v>
       </c>
       <c r="D9" t="n">
-        <v>20.00995841822868</v>
+        <v>3.25161824296216</v>
       </c>
       <c r="E9" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F9" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>3.525375384967999</v>
+        <v>0.5728735000572999</v>
       </c>
       <c r="D10" t="n">
-        <v>4.348755138891457</v>
+        <v>0.7066727100698618</v>
       </c>
       <c r="E10" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F10" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.14715283612299</v>
+        <v>10.09891233586999</v>
       </c>
       <c r="D11" t="n">
-        <v>62.61647716132625</v>
+        <v>10.17517753871552</v>
       </c>
       <c r="E11" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F11" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.15954426611899</v>
+        <v>1.975925943244336</v>
       </c>
       <c r="D12" t="n">
-        <v>11.58642754920775</v>
+        <v>1.88279447674626</v>
       </c>
       <c r="E12" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F12" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.84067484939337</v>
+        <v>1.924109663026423</v>
       </c>
       <c r="D13" t="n">
-        <v>17.75155204823555</v>
+        <v>2.884627207838277</v>
       </c>
       <c r="E13" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F13" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>47.3230223188235</v>
+        <v>7.689991126808819</v>
       </c>
       <c r="D14" t="n">
-        <v>47.88694070723565</v>
+        <v>7.781627864925794</v>
       </c>
       <c r="E14" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F14" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>26.54851899435233</v>
+        <v>4.314134336582254</v>
       </c>
       <c r="D15" t="n">
-        <v>27.24177057502904</v>
+        <v>4.42678771844222</v>
       </c>
       <c r="E15" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F15" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>25.94224354214569</v>
+        <v>4.215614575598675</v>
       </c>
       <c r="D16" t="n">
-        <v>28.58893284975836</v>
+        <v>4.645701588085734</v>
       </c>
       <c r="E16" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F16" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.25754023337075</v>
+        <v>5.079350287922748</v>
       </c>
       <c r="D17" t="n">
-        <v>31.91090362339143</v>
+        <v>5.185521838801108</v>
       </c>
       <c r="E17" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F17" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>50.27803659704638</v>
+        <v>8.170180947020038</v>
       </c>
       <c r="D18" t="n">
-        <v>51.06954021017852</v>
+        <v>8.29880028415401</v>
       </c>
       <c r="E18" t="n">
-        <v>19.36205530861743</v>
+        <v>3.146333987650332</v>
       </c>
       <c r="F18" t="n">
-        <v>18.48357712208162</v>
+        <v>3.003581282338263</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
